--- a/Excel/Luoghi.xlsx
+++ b/Excel/Luoghi.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\umbov\Desktop\Progetto_Vegna_DH\Sito_web\Dati\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\umbov\Desktop\Sito_web\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51A4593D-4768-438C-BC6A-F29C834F8994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6874C14-C4C3-43ED-B65A-43E1A023AA03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4110" yWindow="4110" windowWidth="21600" windowHeight="11385" xr2:uid="{DE613262-B252-4944-9B1A-42A6BD2C95E6}"/>
+    <workbookView xWindow="14400" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{DE613262-B252-4944-9B1A-42A6BD2C95E6}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="70">
   <si>
     <t>luogo</t>
   </si>
@@ -246,6 +246,9 @@
   </si>
   <si>
     <t>record_autorità</t>
+  </si>
+  <si>
+    <t>https://vegnachristian14.github.io/Prima-Repubblica-prime-elezioni/Item_1.html</t>
   </si>
 </sst>
 </file>
@@ -709,7 +712,7 @@
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>3</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -723,7 +726,7 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>3</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -737,7 +740,7 @@
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>3</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
